--- a/results/tscv/consolidated/Stylized_Facts.xlsx
+++ b/results/tscv/consolidated/Stylized_Facts.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Asset</t>
   </si>
@@ -66,6 +66,15 @@
     <t xml:space="preserve">MSFT</t>
   </si>
   <si>
+    <t xml:space="preserve">PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WMT</t>
+  </si>
+  <si>
     <t xml:space="preserve">AMZN</t>
   </si>
   <si>
@@ -78,7 +87,16 @@
     <t xml:space="preserve">GBPUSD</t>
   </si>
   <si>
+    <t xml:space="preserve">GBPCNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">USDZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBPZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EURZAR</t>
   </si>
   <si>
     <t xml:space="preserve">mean_volatility_clustering</t>
@@ -559,40 +577,40 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>1.42289643529993</v>
+        <v>3.58882803101672</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0976726342574077</v>
+        <v>0.335162865686124</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0253450425101044</v>
+        <v>0.0272088395677601</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0111787690484504</v>
+        <v>-0.0859704942449724</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0976726342574077</v>
+        <v>0.335162865686124</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0183150901908193</v>
+        <v>0.0681231909447259</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0167107769685885</v>
+        <v>0.00787197243611168</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0160545213856115</v>
+        <v>0.00806895181087429</v>
       </c>
       <c r="M4" t="n">
-        <v>0.960728601416283</v>
+        <v>1.02502287404603</v>
       </c>
       <c r="N4" t="n">
-        <v>0.394630901869621</v>
+        <v>-0.124229866322706</v>
       </c>
     </row>
     <row r="5">
@@ -600,131 +618,395 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>2.17245464849179</v>
+        <v>2.4346854860285</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.251590040437905</v>
+        <v>0.109860585637237</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0112464210646404</v>
+        <v>0.0166623898183484</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.00462174100455312</v>
+        <v>0.0116020193472119</v>
       </c>
       <c r="I5" t="n">
-        <v>0.251590040437905</v>
+        <v>0.109860585637237</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0627175261494453</v>
+        <v>0.0296108146674977</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00419483935609617</v>
+        <v>0.0144161302054454</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00433002033385744</v>
+        <v>0.0145286597318472</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03222554340843</v>
+        <v>1.00780580674551</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.092916890218104</v>
+        <v>-0.249867540424256</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>1.87447132794184</v>
+        <v>1.92976640697293</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.174912194062967</v>
+        <v>0.201379242618182</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0010287207461143</v>
+        <v>0.0110159281650618</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0380717209398766</v>
+        <v>-0.0519979245358446</v>
       </c>
       <c r="I6" t="n">
-        <v>0.174912194062967</v>
+        <v>0.201379242618182</v>
       </c>
       <c r="J6" t="n">
-        <v>0.104624803000971</v>
+        <v>0.0840236050141599</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00440752811612117</v>
+        <v>0.00878500218924744</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00458777475492328</v>
+        <v>0.00882219006113498</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04089517617433</v>
+        <v>1.00423310900628</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.966041156112683</v>
+        <v>-0.037943189649782</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.42289643529993</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0976726342574077</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0253450425101044</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.0111787690484504</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.0976726342574077</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0183150901908193</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0167107769685885</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0160545213856115</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.960728601416283</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.394630901869621</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.17245464849179</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.251590040437905</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.0112464210646404</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.00462174100455312</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.251590040437905</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0627175261494453</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.00419483935609617</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.00433002033385744</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.03222554340843</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.092916890218104</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.87447132794184</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.174912194062967</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0010287207461143</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0380717209398766</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.174912194062967</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.104624803000971</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.00440752811612117</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.00458777475492328</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.04089517617433</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.966041156112683</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.81569930760892</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.132941818437533</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0020407417416539</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0132566084593931</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.132941818437533</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0309735864207242</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.00429614736740272</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.00454667077720053</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05831350472255</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.547514238087334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="n">
         <v>2.47552084850278</v>
       </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.19207765338689</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F11" t="n">
         <v>-0.0136036994425159</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G11" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H11" t="n">
         <v>-0.030967432749223</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I11" t="n">
         <v>0.19207765338689</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J11" t="n">
         <v>0.0151442732823475</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K11" t="n">
         <v>0.00863299244398515</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L11" t="n">
         <v>0.00766721558342176</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M11" t="n">
         <v>0.888129537141403</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N11" t="n">
         <v>0.555166306307948</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.98280231215248</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.127552726939564</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.013902582038032</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.00661330210837428</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.127552726939564</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.0333863230926924</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.00772596050432598</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.00698277498016001</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.903806714550271</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.611276749043579</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.02172625427921</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.121044377933702</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.0192003320422538</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.0128543070935487</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.121044377933702</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.0198621562192203</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.00757390983398563</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.00672174449543565</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.887486733110269</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.707285428622542</v>
       </c>
     </row>
   </sheetData>
@@ -743,16 +1025,16 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
@@ -760,33 +1042,33 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>1.81708516810632</v>
+        <v>2.23408923805618</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0261299191015978</v>
+        <v>0.0222128191426606</v>
       </c>
       <c r="D2" t="n">
-        <v>0.974976454798557</v>
+        <v>0.993665192365582</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0125342051931825</v>
+        <v>-0.0624063301361994</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
-        <v>2.17414894164547</v>
+        <v>2.0571124498295</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.007940466587014</v>
+        <v>-0.00914726201661231</v>
       </c>
       <c r="D3" t="n">
-        <v>0.987083418908056</v>
+        <v>0.968476201517876</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.167930580007613</v>
+        <v>0.0445426999259914</v>
       </c>
     </row>
   </sheetData>
